--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:09:55+00:00</t>
+    <t>2026-08-20T16:34:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$116</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4866" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4088" uniqueCount="696">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:34:37+00:00</t>
+    <t>2026-08-21T09:28:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -933,6 +933,14 @@
     <t>Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R354-TypeIdentifiantRessourceOperationnelle/FHIR/TRE-R354-TypeIdentifiantRessourceOperationnelle"/&gt;
+    &lt;code value="26"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
@@ -940,199 +948,6 @@
   </si>
   <si>
     <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.id</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.extension</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding.id</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding.system</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding.version</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding.code</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding.display</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Location.identifier:idExterneSynchro.type.text</t>
-  </si>
-  <si>
-    <t>Location.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Location.identifier:idExterneSynchro.system</t>
@@ -1269,40 +1084,12 @@
     <t>Location.identifier:idLocation.type</t>
   </si>
   <si>
-    <t>Location.identifier:idLocation.type.id</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.extension</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding.id</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding.system</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding.version</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding.code</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding.display</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Location.identifier:idLocation.type.text</t>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://mos.esante.gouv.fr/NOS/TRE_R354-TypeIdentifiantRessourceOperationnelle/FHIR/TRE-R354-TypeIdentifiantRessourceOperationnelle"/&gt;
+    &lt;code value="25"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Location.identifier:idLocation.system</t>
@@ -1539,6 +1326,9 @@
   </si>
   <si>
     <t>Telecommunications form for contact point - what communications system is required to make use of the contact.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Telecommunications form for contact point.</t>
@@ -2342,6 +2132,10 @@
   </si>
   <si>
     <t>Location.hoursOfOperation.allDay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
   </si>
   <si>
     <t>The Location is open all day</t>
@@ -2709,7 +2503,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM138"/>
+  <dimension ref="A1:AM116"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.80859375" customWidth="true" bestFit="true"/>
@@ -6578,7 +6372,7 @@
         <v>75</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>75</v>
+        <v>293</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>75</v>
@@ -6596,10 +6390,10 @@
         <v>151</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -6617,7 +6411,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6643,10 +6437,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6666,19 +6460,23 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>102</v>
+        <v>299</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -6690,7 +6488,7 @@
         <v>75</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>75</v>
+        <v>303</v>
       </c>
       <c r="U36" t="s" s="2">
         <v>75</v>
@@ -6726,7 +6524,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>104</v>
+        <v>304</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6735,16 +6533,16 @@
         <v>85</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>105</v>
+        <v>305</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>75</v>
@@ -6752,21 +6550,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -6775,19 +6573,19 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>109</v>
+        <v>308</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>110</v>
+        <v>309</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>111</v>
+        <v>310</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6801,7 +6599,7 @@
         <v>75</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>75</v>
@@ -6825,37 +6623,37 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>115</v>
+        <v>312</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>198</v>
+        <v>313</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>75</v>
@@ -6863,10 +6661,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6877,7 +6675,7 @@
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
@@ -6889,20 +6687,18 @@
         <v>86</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>147</v>
+        <v>316</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
@@ -6950,25 +6746,25 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>75</v>
@@ -6976,10 +6772,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6999,18 +6795,20 @@
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>101</v>
+        <v>325</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>327</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -7059,7 +6857,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>104</v>
+        <v>329</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -7068,61 +6866,63 @@
         <v>85</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>75</v>
+        <v>330</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>105</v>
+        <v>331</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C40" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>333</v>
+      </c>
       <c r="D40" t="s" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>108</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>109</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O40" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
@@ -7158,19 +6958,19 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>115</v>
+        <v>261</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -7179,27 +6979,27 @@
         <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>75</v>
+        <v>335</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>198</v>
+        <v>267</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>75</v>
+        <v>268</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7219,23 +7019,19 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>102</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -7283,7 +7079,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>318</v>
+        <v>104</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7292,16 +7088,16 @@
         <v>85</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>319</v>
+        <v>105</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>75</v>
@@ -7309,21 +7105,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>321</v>
+        <v>275</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -7332,19 +7128,19 @@
         <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>322</v>
+        <v>109</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>323</v>
+        <v>110</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>324</v>
+        <v>111</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7382,37 +7178,37 @@
         <v>75</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>325</v>
+        <v>115</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>326</v>
+        <v>198</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>75</v>
@@ -7420,10 +7216,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>328</v>
+        <v>277</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7431,7 +7227,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>85</v>
@@ -7440,7 +7236,7 @@
         <v>75</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>86</v>
@@ -7449,16 +7245,16 @@
         <v>175</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>329</v>
+        <v>278</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>330</v>
+        <v>279</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -7468,7 +7264,7 @@
         <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>333</v>
+        <v>75</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>75</v>
@@ -7483,13 +7279,13 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>75</v>
+        <v>282</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>75</v>
+        <v>283</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -7507,7 +7303,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>334</v>
+        <v>284</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7525,18 +7321,18 @@
         <v>75</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>335</v>
+        <v>285</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>287</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7544,13 +7340,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>75</v>
@@ -7559,19 +7355,19 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>331</v>
+        <v>291</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>340</v>
+        <v>292</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -7581,7 +7377,7 @@
         <v>75</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>75</v>
@@ -7596,13 +7392,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>75</v>
+        <v>294</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>75</v>
+        <v>295</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -7620,7 +7416,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>341</v>
+        <v>296</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7638,7 +7434,7 @@
         <v>75</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>342</v>
+        <v>285</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>75</v>
@@ -7646,10 +7442,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>298</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7672,19 +7468,19 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>345</v>
+        <v>130</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>346</v>
+        <v>299</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>347</v>
+        <v>300</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>348</v>
+        <v>301</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -7697,7 +7493,7 @@
         <v>75</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>75</v>
+        <v>303</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>75</v>
@@ -7733,7 +7529,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>350</v>
+        <v>304</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -7751,7 +7547,7 @@
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>351</v>
+        <v>305</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
@@ -7759,10 +7555,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>307</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7788,17 +7584,15 @@
         <v>101</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>354</v>
+        <v>308</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>355</v>
+        <v>309</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -7810,7 +7604,7 @@
         <v>75</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>75</v>
+        <v>311</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>75</v>
@@ -7846,7 +7640,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7864,7 +7658,7 @@
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>75</v>
@@ -7872,10 +7666,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>361</v>
+        <v>315</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7898,20 +7692,18 @@
         <v>86</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>130</v>
+        <v>316</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>362</v>
+        <v>317</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -7923,7 +7715,7 @@
         <v>75</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>366</v>
+        <v>75</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>75</v>
@@ -7959,7 +7751,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>320</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -7971,13 +7763,13 @@
         <v>209</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>368</v>
+        <v>322</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>75</v>
@@ -7985,10 +7777,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>369</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>370</v>
+        <v>324</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8011,16 +7803,16 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>101</v>
+        <v>325</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>371</v>
+        <v>326</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>372</v>
+        <v>327</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>373</v>
+        <v>328</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8034,7 +7826,7 @@
         <v>75</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>374</v>
+        <v>75</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>75</v>
@@ -8070,7 +7862,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>375</v>
+        <v>329</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -8082,13 +7874,13 @@
         <v>209</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>330</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>376</v>
+        <v>331</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>75</v>
@@ -8096,10 +7888,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>378</v>
+        <v>345</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8116,23 +7908,21 @@
         <v>75</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>379</v>
+        <v>175</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>380</v>
+        <v>346</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>75</v>
@@ -8157,13 +7947,13 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>75</v>
+        <v>349</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -8181,7 +7971,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>383</v>
+        <v>345</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8190,27 +7980,27 @@
         <v>85</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>385</v>
+        <v>351</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>387</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8224,7 +8014,7 @@
         <v>85</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>75</v>
@@ -8233,17 +8023,15 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>388</v>
+        <v>147</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>389</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>391</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -8268,13 +8056,11 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>75</v>
+        <v>356</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -8292,7 +8078,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>392</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8301,31 +8087,29 @@
         <v>85</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>393</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>75</v>
+        <v>357</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>394</v>
+        <v>105</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>75</v>
+        <v>352</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
@@ -8346,18 +8130,18 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>262</v>
+        <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>359</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>75</v>
       </c>
@@ -8405,13 +8189,13 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>261</v>
+        <v>358</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>75</v>
@@ -8420,21 +8204,21 @@
         <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>398</v>
+        <v>362</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>267</v>
+        <v>363</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>399</v>
+        <v>364</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>273</v>
+        <v>364</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8445,7 +8229,7 @@
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -8460,13 +8244,17 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>102</v>
+        <v>365</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>75</v>
       </c>
@@ -8502,62 +8290,64 @@
         <v>75</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>75</v>
+        <v>369</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>104</v>
+        <v>364</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>105</v>
+        <v>363</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>364</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="D53" t="s" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
@@ -8566,18 +8356,20 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>109</v>
+        <v>365</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
       </c>
@@ -8613,19 +8405,19 @@
         <v>75</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>115</v>
+        <v>364</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8634,27 +8426,27 @@
         <v>77</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>75</v>
+        <v>371</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>198</v>
+        <v>363</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>277</v>
+        <v>372</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8668,28 +8460,26 @@
         <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>278</v>
+        <v>373</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>281</v>
+        <v>375</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -8714,13 +8504,13 @@
         <v>75</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>282</v>
+        <v>75</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>283</v>
+        <v>75</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>75</v>
@@ -8738,7 +8528,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8747,27 +8537,27 @@
         <v>85</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>75</v>
+        <v>376</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>287</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8775,13 +8565,13 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>75</v>
@@ -8790,19 +8580,19 @@
         <v>86</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>288</v>
+        <v>175</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>289</v>
+        <v>379</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>290</v>
+        <v>380</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>291</v>
+        <v>381</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>292</v>
+        <v>382</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -8827,13 +8617,13 @@
         <v>75</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>293</v>
+        <v>380</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>294</v>
+        <v>383</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -8851,7 +8641,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>295</v>
+        <v>378</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8860,7 +8650,7 @@
         <v>85</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>98</v>
@@ -8869,18 +8659,18 @@
         <v>75</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>285</v>
+        <v>384</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>75</v>
+        <v>385</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>297</v>
+        <v>386</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8894,22 +8684,22 @@
         <v>85</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>102</v>
+        <v>387</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>103</v>
+        <v>388</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8936,13 +8726,11 @@
         <v>75</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>75</v>
+        <v>389</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>75</v>
@@ -8960,40 +8748,40 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>104</v>
+        <v>386</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>75</v>
+        <v>390</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>105</v>
+        <v>391</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>75</v>
+        <v>385</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>299</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9003,7 +8791,7 @@
         <v>77</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>75</v>
@@ -9012,17 +8800,15 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>108</v>
+        <v>393</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>109</v>
+        <v>394</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>395</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -9059,19 +8845,19 @@
         <v>75</v>
       </c>
       <c r="AB57" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC57" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>115</v>
+        <v>392</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -9080,16 +8866,16 @@
         <v>77</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>75</v>
+        <v>396</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>198</v>
+        <v>397</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>75</v>
@@ -9097,10 +8883,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>301</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9111,7 +8897,7 @@
         <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>75</v>
@@ -9120,23 +8906,19 @@
         <v>75</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>302</v>
+        <v>102</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>75</v>
       </c>
@@ -9184,25 +8966,25 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>306</v>
+        <v>104</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>307</v>
+        <v>105</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>75</v>
@@ -9210,10 +8992,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>309</v>
+        <v>399</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9221,10 +9003,10 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>76</v>
+        <v>200</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
@@ -9236,13 +9018,13 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>102</v>
+        <v>201</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -9281,62 +9063,64 @@
         <v>75</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>401</v>
+      </c>
       <c r="D60" t="s" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>75</v>
@@ -9345,17 +9129,15 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>108</v>
+        <v>402</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>109</v>
+        <v>403</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N60" s="2"/>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>75</v>
@@ -9392,16 +9174,16 @@
         <v>75</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>115</v>
@@ -9422,20 +9204,22 @@
         <v>75</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>75</v>
       </c>
@@ -9447,29 +9231,25 @@
         <v>85</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>130</v>
+        <v>407</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>314</v>
+        <v>408</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>317</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
       </c>
@@ -9517,69 +9297,69 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>318</v>
+        <v>115</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>319</v>
+        <v>75</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>411</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>101</v>
+        <v>412</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>322</v>
+        <v>413</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>414</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -9628,25 +9408,25 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>325</v>
+        <v>115</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>326</v>
+        <v>75</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>75</v>
@@ -9654,10 +9434,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>328</v>
+        <v>415</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9665,7 +9445,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>85</v>
@@ -9683,17 +9463,15 @@
         <v>175</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>329</v>
+        <v>416</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>330</v>
+        <v>417</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>75</v>
       </c>
@@ -9702,7 +9480,7 @@
         <v>75</v>
       </c>
       <c r="S63" t="s" s="2">
-        <v>411</v>
+        <v>75</v>
       </c>
       <c r="T63" t="s" s="2">
         <v>75</v>
@@ -9717,13 +9495,13 @@
         <v>75</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>75</v>
+        <v>419</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>75</v>
@@ -9741,7 +9519,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>334</v>
+        <v>421</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -9750,7 +9528,7 @@
         <v>85</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>209</v>
+        <v>422</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>98</v>
@@ -9759,18 +9537,18 @@
         <v>75</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>335</v>
+        <v>423</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>337</v>
+        <v>424</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9778,13 +9556,13 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>75</v>
@@ -9796,16 +9574,16 @@
         <v>101</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>338</v>
+        <v>425</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>339</v>
+        <v>426</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>331</v>
+        <v>427</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>340</v>
+        <v>428</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>75</v>
@@ -9854,7 +9632,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>341</v>
+        <v>429</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
@@ -9869,10 +9647,10 @@
         <v>98</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>75</v>
+        <v>430</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>342</v>
+        <v>431</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>75</v>
@@ -9880,10 +9658,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>413</v>
+        <v>432</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>344</v>
+        <v>432</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9900,25 +9678,25 @@
         <v>75</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>345</v>
+        <v>175</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>346</v>
+        <v>433</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>347</v>
+        <v>434</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>348</v>
+        <v>435</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>349</v>
+        <v>436</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>75</v>
@@ -9943,13 +9721,13 @@
         <v>75</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>75</v>
+        <v>437</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>75</v>
+        <v>438</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>75</v>
@@ -9967,7 +9745,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>350</v>
+        <v>439</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -9985,7 +9763,7 @@
         <v>75</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>351</v>
+        <v>440</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>75</v>
@@ -9993,10 +9771,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10019,20 +9797,18 @@
         <v>86</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>101</v>
+        <v>442</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>354</v>
+        <v>443</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>355</v>
+        <v>444</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>75</v>
       </c>
@@ -10080,7 +9856,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>358</v>
+        <v>446</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10098,7 +9874,7 @@
         <v>75</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>359</v>
+        <v>105</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>75</v>
@@ -10106,10 +9882,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>415</v>
+        <v>447</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>361</v>
+        <v>447</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10132,20 +9908,18 @@
         <v>86</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>130</v>
+        <v>316</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>362</v>
+        <v>448</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>363</v>
+        <v>449</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>75</v>
       </c>
@@ -10157,7 +9931,7 @@
         <v>75</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>366</v>
+        <v>75</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>75</v>
@@ -10193,7 +9967,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>367</v>
+        <v>450</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10205,13 +9979,13 @@
         <v>209</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>368</v>
+        <v>451</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>75</v>
@@ -10219,10 +9993,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>416</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>370</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10242,21 +10016,23 @@
         <v>75</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>101</v>
+        <v>453</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>371</v>
+        <v>454</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>372</v>
+        <v>455</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
       </c>
@@ -10268,7 +10044,7 @@
         <v>75</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>374</v>
+        <v>75</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>75</v>
@@ -10304,7 +10080,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>375</v>
+        <v>452</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10313,16 +10089,16 @@
         <v>85</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>75</v>
+        <v>458</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>376</v>
+        <v>459</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>75</v>
@@ -10330,10 +10106,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>417</v>
+        <v>460</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>378</v>
+        <v>460</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10353,20 +10129,18 @@
         <v>75</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>379</v>
+        <v>101</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>380</v>
+        <v>102</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>75</v>
@@ -10415,7 +10189,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10424,16 +10198,16 @@
         <v>85</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>384</v>
+        <v>75</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>385</v>
+        <v>105</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>75</v>
@@ -10441,21 +10215,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>387</v>
+        <v>461</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>75</v>
@@ -10464,19 +10238,19 @@
         <v>75</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>388</v>
+        <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>389</v>
+        <v>109</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>391</v>
+        <v>111</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10514,37 +10288,37 @@
         <v>75</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>392</v>
+        <v>115</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>393</v>
+        <v>116</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>394</v>
+        <v>198</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>75</v>
@@ -10552,10 +10326,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10581,13 +10355,17 @@
         <v>175</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>420</v>
+        <v>463</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>75</v>
       </c>
@@ -10599,7 +10377,7 @@
         <v>75</v>
       </c>
       <c r="T71" t="s" s="2">
-        <v>75</v>
+        <v>467</v>
       </c>
       <c r="U71" t="s" s="2">
         <v>75</v>
@@ -10614,10 +10392,10 @@
         <v>166</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>422</v>
+        <v>468</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>423</v>
+        <v>469</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>75</v>
@@ -10635,7 +10413,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>419</v>
+        <v>470</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10644,27 +10422,27 @@
         <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>424</v>
+        <v>75</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>426</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>427</v>
+        <v>471</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10678,7 +10456,7 @@
         <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>75</v>
@@ -10687,15 +10465,17 @@
         <v>86</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>473</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>474</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>75</v>
@@ -10708,7 +10488,7 @@
         <v>75</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>75</v>
+        <v>475</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>75</v>
@@ -10722,9 +10502,11 @@
       <c r="X72" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Y72" s="2"/>
+      <c r="Y72" t="s" s="2">
+        <v>476</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>430</v>
+        <v>477</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>75</v>
@@ -10742,7 +10524,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>427</v>
+        <v>478</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
@@ -10751,27 +10533,27 @@
         <v>85</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>431</v>
+        <v>75</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>105</v>
+        <v>440</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>426</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>432</v>
+        <v>479</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>432</v>
+        <v>479</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10785,7 +10567,7 @@
         <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
@@ -10797,15 +10579,17 @@
         <v>101</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>433</v>
+        <v>480</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>434</v>
+        <v>481</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>75</v>
       </c>
@@ -10817,7 +10601,7 @@
         <v>75</v>
       </c>
       <c r="T73" t="s" s="2">
-        <v>75</v>
+        <v>484</v>
       </c>
       <c r="U73" t="s" s="2">
         <v>75</v>
@@ -10853,7 +10637,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>432</v>
+        <v>485</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -10862,16 +10646,16 @@
         <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>436</v>
+        <v>75</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>437</v>
+        <v>486</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>75</v>
@@ -10879,10 +10663,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>438</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>438</v>
+        <v>487</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10902,23 +10686,21 @@
         <v>75</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>439</v>
+        <v>488</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>440</v>
+        <v>489</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>75</v>
       </c>
@@ -10930,7 +10712,7 @@
         <v>75</v>
       </c>
       <c r="T74" t="s" s="2">
-        <v>75</v>
+        <v>490</v>
       </c>
       <c r="U74" t="s" s="2">
         <v>75</v>
@@ -10954,19 +10736,19 @@
         <v>75</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>443</v>
+        <v>75</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>438</v>
+        <v>491</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -10975,7 +10757,7 @@
         <v>77</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>98</v>
@@ -10984,22 +10766,20 @@
         <v>75</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>437</v>
+        <v>492</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>444</v>
+        <v>493</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C75" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>493</v>
+      </c>
+      <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>75</v>
       </c>
@@ -11011,7 +10791,7 @@
         <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>75</v>
@@ -11023,17 +10803,13 @@
         <v>101</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>439</v>
+        <v>102</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>75</v>
       </c>
@@ -11081,70 +10857,70 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>438</v>
+        <v>104</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>445</v>
+        <v>75</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>437</v>
+        <v>105</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>446</v>
+        <v>494</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>446</v>
+        <v>494</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>447</v>
+        <v>109</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>75</v>
       </c>
@@ -11180,50 +10956,52 @@
         <v>75</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>446</v>
+        <v>115</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>450</v>
+        <v>75</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>451</v>
+        <v>198</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>496</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
@@ -11235,29 +11013,25 @@
         <v>85</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>175</v>
+        <v>497</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>453</v>
+        <v>498</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>75</v>
       </c>
@@ -11281,13 +11055,13 @@
         <v>75</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>454</v>
+        <v>75</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>457</v>
+        <v>75</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>75</v>
@@ -11305,38 +11079,40 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>452</v>
+        <v>115</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>458</v>
+        <v>501</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>459</v>
+        <v>75</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>460</v>
+        <v>502</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>503</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
@@ -11354,16 +11130,16 @@
         <v>75</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>288</v>
+        <v>504</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>461</v>
+        <v>505</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>462</v>
+        <v>506</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11390,11 +11166,13 @@
         <v>75</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>463</v>
+        <v>75</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>75</v>
@@ -11412,7 +11190,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>460</v>
+        <v>115</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11421,29 +11199,31 @@
         <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>464</v>
+        <v>507</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>465</v>
+        <v>508</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>459</v>
+        <v>75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>466</v>
+        <v>509</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
@@ -11452,7 +11232,7 @@
         <v>76</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>86</v>
@@ -11464,13 +11244,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>467</v>
+        <v>511</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>468</v>
+        <v>512</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>469</v>
+        <v>513</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11521,7 +11301,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>466</v>
+        <v>115</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11530,29 +11310,31 @@
         <v>77</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>470</v>
+        <v>514</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>471</v>
+        <v>515</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
-        <v>472</v>
+        <v>516</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="C80" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
@@ -11564,7 +11346,7 @@
         <v>85</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
@@ -11573,13 +11355,13 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>101</v>
+        <v>518</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>102</v>
+        <v>519</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>103</v>
+        <v>520</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11630,50 +11412,52 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>75</v>
+        <v>521</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
-        <v>473</v>
+        <v>523</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>524</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>75</v>
@@ -11682,13 +11466,13 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>108</v>
+        <v>525</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>201</v>
+        <v>526</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>202</v>
+        <v>527</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -11727,16 +11511,16 @@
         <v>75</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
         <v>115</v>
@@ -11754,37 +11538,35 @@
         <v>116</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>75</v>
+        <v>528</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>75</v>
+        <v>529</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C82" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>75</v>
@@ -11793,13 +11575,13 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>476</v>
+        <v>101</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>477</v>
+        <v>102</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>478</v>
+        <v>103</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11850,40 +11632,38 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>479</v>
+        <v>532</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C83" t="s" s="2">
-        <v>480</v>
-      </c>
+        <v>533</v>
+      </c>
+      <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>75</v>
       </c>
@@ -11892,10 +11672,10 @@
         <v>76</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>75</v>
@@ -11904,13 +11684,13 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>481</v>
+        <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>482</v>
+        <v>201</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>483</v>
+        <v>202</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11949,16 +11729,16 @@
         <v>75</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AF83" t="s" s="2">
         <v>115</v>
@@ -11970,7 +11750,7 @@
         <v>77</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>116</v>
@@ -11985,16 +11765,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>534</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="C84" t="s" s="2">
-        <v>485</v>
-      </c>
+        <v>535</v>
+      </c>
+      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>75</v>
       </c>
@@ -12006,7 +11784,7 @@
         <v>85</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>75</v>
@@ -12015,22 +11793,24 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>486</v>
+        <v>130</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>487</v>
+        <v>536</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>537</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>538</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>75</v>
+        <v>539</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>75</v>
@@ -12072,25 +11852,25 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>115</v>
+        <v>540</v>
       </c>
       <c r="AG84" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>75</v>
@@ -12098,10 +11878,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>489</v>
+        <v>541</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>489</v>
+        <v>542</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12109,7 +11889,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>85</v>
@@ -12121,20 +11901,18 @@
         <v>75</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>490</v>
+        <v>543</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>75</v>
@@ -12161,11 +11939,9 @@
       <c r="X85" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Y85" t="s" s="2">
-        <v>492</v>
-      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>493</v>
+        <v>545</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -12183,7 +11959,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>494</v>
+        <v>546</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12192,7 +11968,7 @@
         <v>85</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>495</v>
+        <v>75</v>
       </c>
       <c r="AJ85" t="s" s="2">
         <v>98</v>
@@ -12201,7 +11977,7 @@
         <v>75</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>496</v>
+        <v>198</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>75</v>
@@ -12209,18 +11985,20 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>497</v>
+        <v>547</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s" s="2">
         <v>85</v>
@@ -12232,23 +12010,19 @@
         <v>75</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>101</v>
+        <v>549</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>498</v>
+        <v>550</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>501</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>75</v>
       </c>
@@ -12296,38 +12070,40 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>502</v>
+        <v>115</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>503</v>
+        <v>552</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>504</v>
+        <v>553</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
-        <v>505</v>
+        <v>554</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>555</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
@@ -12339,29 +12115,25 @@
         <v>85</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>175</v>
+        <v>556</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>506</v>
+        <v>557</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>509</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>75</v>
       </c>
@@ -12385,13 +12157,13 @@
         <v>75</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>510</v>
+        <v>75</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>511</v>
+        <v>75</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>75</v>
@@ -12409,38 +12181,40 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>512</v>
+        <v>115</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>75</v>
+        <v>559</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>513</v>
+        <v>560</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
-        <v>514</v>
+        <v>561</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>494</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="D88" t="s" s="2">
         <v>75</v>
       </c>
@@ -12452,26 +12226,24 @@
         <v>85</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>515</v>
+        <v>563</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>516</v>
+        <v>564</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>565</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>75</v>
@@ -12520,25 +12292,25 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>519</v>
+        <v>115</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>75</v>
+        <v>562</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>75</v>
@@ -12546,10 +12318,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>520</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>520</v>
+        <v>566</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12569,20 +12341,18 @@
         <v>75</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>379</v>
+        <v>101</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>521</v>
+        <v>567</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>382</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>75</v>
@@ -12604,7 +12374,7 @@
         <v>75</v>
       </c>
       <c r="W89" t="s" s="2">
-        <v>75</v>
+        <v>568</v>
       </c>
       <c r="X89" t="s" s="2">
         <v>75</v>
@@ -12631,7 +12401,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>523</v>
+        <v>569</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12640,16 +12410,16 @@
         <v>85</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>384</v>
+        <v>75</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>524</v>
+        <v>75</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>75</v>
@@ -12657,14 +12427,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>525</v>
+        <v>570</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>75</v>
+        <v>571</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12680,23 +12450,21 @@
         <v>75</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>526</v>
+        <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>527</v>
+        <v>572</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>528</v>
+        <v>573</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>75</v>
       </c>
@@ -12708,7 +12476,7 @@
         <v>75</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>75</v>
+        <v>574</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>75</v>
@@ -12744,7 +12512,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>525</v>
+        <v>575</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12753,16 +12521,16 @@
         <v>85</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>531</v>
+        <v>576</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>532</v>
+        <v>577</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>75</v>
@@ -12770,14 +12538,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>578</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>75</v>
+        <v>579</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -12793,18 +12561,20 @@
         <v>75</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K91" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>102</v>
+        <v>580</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>582</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>75</v>
@@ -12817,7 +12587,7 @@
         <v>75</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>75</v>
+        <v>583</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>75</v>
@@ -12853,7 +12623,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>104</v>
+        <v>584</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
@@ -12862,16 +12632,16 @@
         <v>85</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>75</v>
+        <v>209</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>105</v>
+        <v>585</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>75</v>
@@ -12879,21 +12649,21 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>534</v>
+        <v>586</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>534</v>
+        <v>586</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>107</v>
+        <v>587</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>75</v>
@@ -12902,19 +12672,19 @@
         <v>75</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>109</v>
+        <v>588</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>110</v>
+        <v>589</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>111</v>
+        <v>418</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12952,37 +12722,37 @@
         <v>75</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>115</v>
+        <v>590</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>209</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>198</v>
+        <v>591</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>75</v>
@@ -12990,14 +12760,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>535</v>
+        <v>592</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>535</v>
+        <v>592</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>75</v>
+        <v>593</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13010,26 +12780,24 @@
         <v>75</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="J93" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>536</v>
+        <v>594</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>537</v>
+        <v>595</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>539</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>75</v>
       </c>
@@ -13041,7 +12809,7 @@
         <v>75</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>540</v>
+        <v>596</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>75</v>
@@ -13053,13 +12821,13 @@
         <v>75</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>541</v>
+        <v>75</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>542</v>
+        <v>75</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>75</v>
@@ -13077,7 +12845,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>543</v>
+        <v>597</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13092,10 +12860,10 @@
         <v>98</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>75</v>
+        <v>598</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>513</v>
+        <v>599</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>75</v>
@@ -13103,10 +12871,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13129,16 +12897,16 @@
         <v>86</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>545</v>
+        <v>601</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>546</v>
+        <v>602</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>547</v>
+        <v>603</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13152,7 +12920,7 @@
         <v>75</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>548</v>
+        <v>75</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>75</v>
@@ -13164,13 +12932,13 @@
         <v>75</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>166</v>
+        <v>75</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>549</v>
+        <v>75</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>550</v>
+        <v>75</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>75</v>
@@ -13188,7 +12956,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>551</v>
+        <v>604</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -13206,7 +12974,7 @@
         <v>75</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>513</v>
+        <v>605</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>75</v>
@@ -13214,10 +12982,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>552</v>
+        <v>606</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>552</v>
+        <v>606</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13240,19 +13008,19 @@
         <v>86</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>101</v>
+        <v>316</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>553</v>
+        <v>607</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>554</v>
+        <v>608</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>555</v>
+        <v>319</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>556</v>
+        <v>609</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>75</v>
@@ -13265,7 +13033,7 @@
         <v>75</v>
       </c>
       <c r="T95" t="s" s="2">
-        <v>557</v>
+        <v>610</v>
       </c>
       <c r="U95" t="s" s="2">
         <v>75</v>
@@ -13301,7 +13069,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>558</v>
+        <v>611</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13313,13 +13081,13 @@
         <v>209</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>98</v>
+        <v>321</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>559</v>
+        <v>451</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>75</v>
@@ -13327,10 +13095,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>560</v>
+        <v>612</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>560</v>
+        <v>612</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13341,7 +13109,7 @@
         <v>76</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>75</v>
@@ -13353,18 +13121,18 @@
         <v>86</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>561</v>
+        <v>613</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>614</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>75</v>
       </c>
@@ -13376,7 +13144,7 @@
         <v>75</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>563</v>
+        <v>75</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>75</v>
@@ -13388,13 +13156,13 @@
         <v>75</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>75</v>
+        <v>616</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>75</v>
+        <v>617</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>75</v>
@@ -13412,16 +13180,16 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>564</v>
+        <v>612</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>98</v>
@@ -13430,18 +13198,18 @@
         <v>75</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>565</v>
+        <v>618</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>75</v>
+        <v>385</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>566</v>
+        <v>619</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>566</v>
+        <v>619</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13464,16 +13232,18 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>101</v>
+        <v>620</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>102</v>
+        <v>621</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>103</v>
+        <v>622</v>
       </c>
       <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>623</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>75</v>
       </c>
@@ -13521,7 +13291,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>104</v>
+        <v>619</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13533,13 +13303,13 @@
         <v>75</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>75</v>
+        <v>624</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>105</v>
+        <v>625</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>75</v>
@@ -13547,21 +13317,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>567</v>
+        <v>626</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>567</v>
+        <v>626</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>75</v>
@@ -13573,17 +13343,15 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N98" s="2"/>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>75</v>
@@ -13620,52 +13388,50 @@
         <v>75</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>198</v>
+        <v>105</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>568</v>
+        <v>627</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>569</v>
-      </c>
+        <v>627</v>
+      </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
@@ -13674,10 +13440,10 @@
         <v>76</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>75</v>
@@ -13686,13 +13452,13 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>570</v>
+        <v>108</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>571</v>
+        <v>201</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>572</v>
+        <v>202</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13731,16 +13497,14 @@
         <v>75</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="AC99" s="2"/>
       <c r="AD99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>75</v>
+        <v>114</v>
       </c>
       <c r="AF99" t="s" s="2">
         <v>115</v>
@@ -13752,16 +13516,16 @@
         <v>77</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>573</v>
+        <v>75</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>574</v>
+        <v>75</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>75</v>
@@ -13769,13 +13533,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>575</v>
+        <v>628</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>567</v>
+        <v>627</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>576</v>
+        <v>629</v>
       </c>
       <c r="D100" t="s" s="2">
         <v>75</v>
@@ -13797,13 +13561,13 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>577</v>
+        <v>630</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>578</v>
+        <v>631</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>579</v>
+        <v>632</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13869,55 +13633,57 @@
         <v>116</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>580</v>
+        <v>75</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>581</v>
+        <v>75</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>582</v>
+        <v>633</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C101" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>633</v>
+      </c>
+      <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>75</v>
+        <v>634</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H101" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I101" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I101" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="J101" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>584</v>
+        <v>108</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>585</v>
+        <v>635</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+        <v>636</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>75</v>
       </c>
@@ -13965,7 +13731,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>115</v>
+        <v>637</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13974,43 +13740,41 @@
         <v>77</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>587</v>
+        <v>75</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>588</v>
+        <v>198</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>589</v>
+        <v>638</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C102" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>638</v>
+      </c>
+      <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>75</v>
@@ -14019,13 +13783,13 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>591</v>
+        <v>639</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>592</v>
+        <v>640</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>593</v>
+        <v>641</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14076,52 +13840,50 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>115</v>
+        <v>638</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>594</v>
+        <v>642</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>595</v>
+        <v>643</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>596</v>
+        <v>644</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>597</v>
-      </c>
+        <v>644</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>75</v>
@@ -14130,13 +13892,13 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>598</v>
+        <v>639</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>599</v>
+        <v>645</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>600</v>
+        <v>646</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14187,25 +13949,25 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>115</v>
+        <v>644</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>601</v>
+        <v>647</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>75</v>
@@ -14213,10 +13975,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>603</v>
+        <v>648</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>604</v>
+        <v>648</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14239,13 +14001,13 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>101</v>
+        <v>639</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>102</v>
+        <v>649</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>103</v>
+        <v>650</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14296,7 +14058,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>104</v>
+        <v>648</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14308,24 +14070,24 @@
         <v>75</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>105</v>
+        <v>643</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>605</v>
+        <v>651</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>606</v>
+        <v>651</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14336,28 +14098,32 @@
         <v>76</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>108</v>
+        <v>652</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>201</v>
+        <v>653</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>654</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>75</v>
       </c>
@@ -14393,48 +14159,48 @@
         <v>75</v>
       </c>
       <c r="AB105" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>114</v>
+        <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>115</v>
+        <v>651</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>75</v>
+        <v>657</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
-        <v>607</v>
+        <v>658</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>608</v>
+        <v>658</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14442,13 +14208,13 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>85</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>75</v>
@@ -14457,24 +14223,24 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>130</v>
+        <v>659</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>609</v>
+        <v>660</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O106" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>662</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q106" s="2"/>
       <c r="R106" t="s" s="2">
-        <v>612</v>
+        <v>75</v>
       </c>
       <c r="S106" t="s" s="2">
         <v>75</v>
@@ -14516,10 +14282,10 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>613</v>
+        <v>658</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>85</v>
@@ -14528,13 +14294,13 @@
         <v>75</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>198</v>
+        <v>663</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>75</v>
@@ -14542,10 +14308,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>614</v>
+        <v>664</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>615</v>
+        <v>664</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14553,10 +14319,10 @@
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>75</v>
@@ -14568,15 +14334,17 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>101</v>
+        <v>620</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>616</v>
+        <v>665</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>666</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>667</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>75</v>
@@ -14601,11 +14369,13 @@
         <v>75</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>618</v>
+        <v>75</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -14623,13 +14393,13 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>619</v>
+        <v>664</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>75</v>
@@ -14641,22 +14411,20 @@
         <v>75</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>198</v>
+        <v>668</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>620</v>
+        <v>669</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>621</v>
-      </c>
+        <v>669</v>
+      </c>
+      <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>75</v>
       </c>
@@ -14668,7 +14436,7 @@
         <v>85</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>75</v>
@@ -14677,13 +14445,13 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>622</v>
+        <v>101</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>623</v>
+        <v>102</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>624</v>
+        <v>103</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14734,52 +14502,50 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ108" t="s" s="2">
-        <v>116</v>
+        <v>75</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>625</v>
+        <v>75</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>626</v>
+        <v>105</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>627</v>
+        <v>670</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>75</v>
@@ -14788,15 +14554,17 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>629</v>
+        <v>108</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>630</v>
+        <v>109</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>111</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>75</v>
@@ -14854,61 +14622,63 @@
         <v>77</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>632</v>
+        <v>75</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>633</v>
+        <v>105</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="C110" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="D110" t="s" s="2">
-        <v>75</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H110" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I110" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="I110" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="J110" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M110" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L110" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+      <c r="N110" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>75</v>
       </c>
@@ -14956,7 +14726,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>115</v>
+        <v>637</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14965,16 +14735,16 @@
         <v>77</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>116</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>635</v>
+        <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>75</v>
@@ -14982,10 +14752,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>639</v>
+        <v>672</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>639</v>
+        <v>672</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14996,7 +14766,7 @@
         <v>76</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>75</v>
@@ -15008,13 +14778,13 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>640</v>
+        <v>673</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>640</v>
+        <v>674</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15038,16 +14808,16 @@
         <v>75</v>
       </c>
       <c r="W111" t="s" s="2">
-        <v>641</v>
+        <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
+        <v>166</v>
       </c>
       <c r="Y111" t="s" s="2">
-        <v>75</v>
+        <v>675</v>
       </c>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>676</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -15065,25 +14835,25 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>642</v>
+        <v>672</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>75</v>
+        <v>668</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>75</v>
@@ -15091,14 +14861,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>643</v>
+        <v>677</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>643</v>
+        <v>677</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>644</v>
+        <v>75</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15114,20 +14884,18 @@
         <v>75</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>101</v>
+        <v>678</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>645</v>
+        <v>679</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>75</v>
@@ -15140,7 +14908,7 @@
         <v>75</v>
       </c>
       <c r="T112" t="s" s="2">
-        <v>647</v>
+        <v>75</v>
       </c>
       <c r="U112" t="s" s="2">
         <v>75</v>
@@ -15176,7 +14944,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>648</v>
+        <v>677</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15185,16 +14953,16 @@
         <v>85</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ112" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>649</v>
+        <v>75</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>650</v>
+        <v>668</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>75</v>
@@ -15202,14 +14970,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>651</v>
+        <v>681</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>652</v>
+        <v>75</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -15225,20 +14993,18 @@
         <v>75</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>101</v>
+        <v>682</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>653</v>
+        <v>683</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>655</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>75</v>
@@ -15251,7 +15017,7 @@
         <v>75</v>
       </c>
       <c r="T113" t="s" s="2">
-        <v>656</v>
+        <v>75</v>
       </c>
       <c r="U113" t="s" s="2">
         <v>75</v>
@@ -15287,7 +15053,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>657</v>
+        <v>681</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15296,7 +15062,7 @@
         <v>85</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>98</v>
@@ -15305,7 +15071,7 @@
         <v>75</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>658</v>
+        <v>668</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>75</v>
@@ -15313,14 +15079,14 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>659</v>
+        <v>685</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>659</v>
+        <v>685</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>660</v>
+        <v>75</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
@@ -15336,20 +15102,18 @@
         <v>75</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>101</v>
+        <v>682</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>661</v>
+        <v>686</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>75</v>
@@ -15398,7 +15162,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>663</v>
+        <v>685</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15407,7 +15171,7 @@
         <v>85</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>98</v>
@@ -15416,7 +15180,7 @@
         <v>75</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>75</v>
@@ -15424,14 +15188,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>666</v>
+        <v>75</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15447,20 +15211,18 @@
         <v>75</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
         <v>101</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>667</v>
+        <v>689</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>690</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>75</v>
@@ -15473,7 +15235,7 @@
         <v>75</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>669</v>
+        <v>75</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>75</v>
@@ -15509,7 +15271,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>670</v>
+        <v>688</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15518,16 +15280,16 @@
         <v>85</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>671</v>
+        <v>75</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>672</v>
+        <v>105</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>75</v>
@@ -15535,10 +15297,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>673</v>
+        <v>691</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15549,7 +15311,7 @@
         <v>76</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>75</v>
@@ -15558,21 +15320,21 @@
         <v>75</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>101</v>
+        <v>692</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>674</v>
+        <v>693</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="O116" s="2"/>
+        <v>694</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>695</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>75</v>
       </c>
@@ -15620,16 +15382,16 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>677</v>
+        <v>691</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>98</v>
@@ -15638,2440 +15400,14 @@
         <v>75</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>678</v>
+        <v>105</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>684</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" t="s" s="2">
-        <v>688</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>689</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="AC121" s="2"/>
-      <c r="AD121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="C122" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="D122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="O129" s="2"/>
-      <c r="P129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>744</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O132" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>746</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>747</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>748</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>752</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>758</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>761</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>762</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>764</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>765</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" t="s" s="2">
-        <v>767</v>
-      </c>
-      <c r="P138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM138" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AM138">
+  <autoFilter ref="A1:AM116">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18081,7 +15417,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI137">
+  <conditionalFormatting sqref="A2:AI115">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:28:33+00:00</t>
+    <t>2026-08-21T09:39:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T09:39:43+00:00</t>
+    <t>2026-08-21T14:30:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:30:36+00:00</t>
+    <t>2026-08-21T16:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
+++ b/update-dependencies-fr-core-annuaire/ig/StructureDefinition-ror-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:03:39+00:00</t>
+    <t>2026-08-26T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
